--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29 11:20</t>
+    <t xml:space="preserve">2026-08-19 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:19</t>
+    <t xml:space="preserve">2026-08-20 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 12:40</t>
+    <t xml:space="preserve">2026-08-28 15:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:09</t>
+    <t xml:space="preserve">2026-08-29 05:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,13 +474,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4.28</v>
+        <v>8.56</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.56</v>
+        <v>13.12</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2.28</v>
+        <v>4.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_isapre_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:45</t>
+    <t xml:space="preserve">2026-09-07 11:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
